--- a/artfynd/A 43065-2022 artfynd.xlsx
+++ b/artfynd/A 43065-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118443562</v>
+        <v>118443558</v>
       </c>
       <c r="B2" t="n">
-        <v>78220</v>
+        <v>79102</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443054</v>
+        <v>443070</v>
       </c>
       <c r="R2" t="n">
-        <v>6674687</v>
+        <v>6674646</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118443558</v>
+        <v>118443562</v>
       </c>
       <c r="B3" t="n">
-        <v>79102</v>
+        <v>78220</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443070</v>
+        <v>443054</v>
       </c>
       <c r="R3" t="n">
-        <v>6674646</v>
+        <v>6674687</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118443557</v>
+        <v>118443560</v>
       </c>
       <c r="B5" t="n">
-        <v>97763</v>
+        <v>79102</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443113</v>
+        <v>443055</v>
       </c>
       <c r="R5" t="n">
-        <v>6674794</v>
+        <v>6674686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118443560</v>
+        <v>118443557</v>
       </c>
       <c r="B6" t="n">
-        <v>79102</v>
+        <v>97763</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443055</v>
+        <v>443113</v>
       </c>
       <c r="R6" t="n">
-        <v>6674686</v>
+        <v>6674794</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 43065-2022 artfynd.xlsx
+++ b/artfynd/A 43065-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118443558</v>
       </c>
       <c r="B2" t="n">
-        <v>79102</v>
+        <v>79109</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>118443562</v>
       </c>
       <c r="B3" t="n">
-        <v>78220</v>
+        <v>78227</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118443561</v>
+        <v>118443557</v>
       </c>
       <c r="B4" t="n">
-        <v>78221</v>
+        <v>97770</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443055</v>
+        <v>443113</v>
       </c>
       <c r="R4" t="n">
-        <v>6674687</v>
+        <v>6674794</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>118443560</v>
       </c>
       <c r="B5" t="n">
-        <v>79102</v>
+        <v>79109</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118443557</v>
+        <v>118443561</v>
       </c>
       <c r="B6" t="n">
-        <v>97763</v>
+        <v>78228</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443113</v>
+        <v>443055</v>
       </c>
       <c r="R6" t="n">
-        <v>6674794</v>
+        <v>6674687</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 43065-2022 artfynd.xlsx
+++ b/artfynd/A 43065-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118443558</v>
+        <v>118443560</v>
       </c>
       <c r="B2" t="n">
         <v>79109</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443070</v>
+        <v>443055</v>
       </c>
       <c r="R2" t="n">
-        <v>6674646</v>
+        <v>6674686</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118443562</v>
+        <v>118443561</v>
       </c>
       <c r="B3" t="n">
-        <v>78227</v>
+        <v>78228</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443054</v>
+        <v>443055</v>
       </c>
       <c r="R3" t="n">
         <v>6674687</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118443557</v>
+        <v>118443558</v>
       </c>
       <c r="B4" t="n">
-        <v>97770</v>
+        <v>79109</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443113</v>
+        <v>443070</v>
       </c>
       <c r="R4" t="n">
-        <v>6674794</v>
+        <v>6674646</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118443560</v>
+        <v>118443562</v>
       </c>
       <c r="B5" t="n">
-        <v>79109</v>
+        <v>78227</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443055</v>
+        <v>443054</v>
       </c>
       <c r="R5" t="n">
-        <v>6674686</v>
+        <v>6674687</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118443561</v>
+        <v>118443557</v>
       </c>
       <c r="B6" t="n">
-        <v>78228</v>
+        <v>97770</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443055</v>
+        <v>443113</v>
       </c>
       <c r="R6" t="n">
-        <v>6674687</v>
+        <v>6674794</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
